--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -33538,7 +33538,7 @@
         </is>
       </c>
       <c r="G204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -33550,24 +33550,24 @@
         <v>0</v>
       </c>
       <c r="K204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L204">
         <v>0</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -33622,7 +33622,7 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "56"]</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
@@ -33640,28 +33640,28 @@
         <v>0</v>
       </c>
       <c r="AM204">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN204">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO204">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP204">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ204">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR204">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS204">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT204">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
@@ -34027,16 +34027,16 @@
         </is>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N207">
@@ -34065,10 +34065,10 @@
         <v>2.17</v>
       </c>
       <c r="S207">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T207">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U207">
         <v>3</v>
@@ -34111,12 +34111,12 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31"]</t>
         </is>
       </c>
       <c r="AJ207">
@@ -34129,28 +34129,28 @@
         <v>0</v>
       </c>
       <c r="AM207">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN207">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO207">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP207">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ207">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR207">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS207">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT207">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
@@ -35322,139 +35322,139 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I215">
         <v>0</v>
       </c>
       <c r="J215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N215">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="O215">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P215">
-        <v>2.6</v>
+        <v>5.53</v>
       </c>
       <c r="Q215">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="R215">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S215">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T215">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U215">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="V215">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W215">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X215">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y215">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z215">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA215">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="AB215">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC215">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD215">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE215">
         <v>1.05</v>
       </c>
       <c r="AF215">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG215">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "90"]</t>
         </is>
       </c>
       <c r="AJ215">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK215">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AL215">
         <v>0</v>
       </c>
       <c r="AM215">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN215">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO215">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP215">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ215">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR215">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS215">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT215">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
@@ -35485,22 +35485,22 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H216">
         <v>0</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216">
         <v>0</v>
@@ -35513,111 +35513,111 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N216">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="O216">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P216">
-        <v>5.53</v>
+        <v>3.6</v>
       </c>
       <c r="Q216">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R216">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S216">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T216">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U216">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="V216">
+        <v>1.29</v>
+      </c>
+      <c r="W216">
+        <v>1.03</v>
+      </c>
+      <c r="X216">
+        <v>1.08</v>
+      </c>
+      <c r="Y216">
         <v>1.36</v>
       </c>
-      <c r="W216">
-        <v>1.07</v>
-      </c>
-      <c r="X216">
-        <v>1.06</v>
-      </c>
-      <c r="Y216">
-        <v>1.3</v>
-      </c>
       <c r="Z216">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA216">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AB216">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC216">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD216">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE216">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF216">
         <v>2</v>
       </c>
       <c r="AG216">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
+          <t>["36"]</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ216">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK216">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL216">
         <v>0</v>
       </c>
       <c r="AM216">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN216">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO216">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP216">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ216">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR216">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS216">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT216">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
@@ -35648,22 +35648,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217">
         <v>0</v>
       </c>
       <c r="I217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -35676,32 +35676,32 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N217">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O217">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="P217">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q217">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R217">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S217">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T217">
         <v>2.63</v>
       </c>
       <c r="U217">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="V217">
         <v>1.29</v>
@@ -35710,7 +35710,7 @@
         <v>1.03</v>
       </c>
       <c r="X217">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y217">
         <v>1.36</v>
@@ -35722,65 +35722,65 @@
         <v>2.25</v>
       </c>
       <c r="AB217">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC217">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AD217">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE217">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF217">
+        <v>1.91</v>
+      </c>
+      <c r="AG217">
+        <v>1.75</v>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>["44"]</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ217">
+        <v>1.33</v>
+      </c>
+      <c r="AK217">
+        <v>1.55</v>
+      </c>
+      <c r="AL217">
+        <v>0</v>
+      </c>
+      <c r="AM217">
+        <v>7</v>
+      </c>
+      <c r="AN217">
+        <v>4</v>
+      </c>
+      <c r="AO217">
+        <v>17</v>
+      </c>
+      <c r="AP217">
+        <v>10</v>
+      </c>
+      <c r="AQ217">
         <v>2</v>
       </c>
-      <c r="AG217">
-        <v>1.67</v>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ217">
-        <v>1.26</v>
-      </c>
-      <c r="AK217">
-        <v>1.73</v>
-      </c>
-      <c r="AL217">
-        <v>0</v>
-      </c>
-      <c r="AM217">
-        <v>-1</v>
-      </c>
-      <c r="AN217">
-        <v>-1</v>
-      </c>
-      <c r="AO217">
-        <v>-1</v>
-      </c>
-      <c r="AP217">
-        <v>-1</v>
-      </c>
-      <c r="AQ217">
-        <v>0</v>
-      </c>
       <c r="AR217">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS217">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT217">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N225">
@@ -37063,28 +37063,28 @@
         <v>0</v>
       </c>
       <c r="AM225">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN225">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO225">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP225">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ225">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR225">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS225">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT225">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
@@ -37124,16 +37124,16 @@
         </is>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K226">
         <v>0</v>
@@ -37143,7 +37143,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N226">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ226">
@@ -37226,28 +37226,28 @@
         <v>0</v>
       </c>
       <c r="AM226">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN226">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO226">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP226">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ226">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR226">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS226">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT226">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
@@ -37287,13 +37287,13 @@
         </is>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227">
         <v>0</v>
@@ -37302,11 +37302,11 @@
         <v>0</v>
       </c>
       <c r="L227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N227">
@@ -37371,12 +37371,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81", "86"]</t>
         </is>
       </c>
       <c r="AJ227">
@@ -37389,28 +37389,28 @@
         <v>0</v>
       </c>
       <c r="AM227">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN227">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO227">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP227">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ227">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR227">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS227">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT227">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
@@ -37450,10 +37450,10 @@
         </is>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -37462,14 +37462,14 @@
         <v>0</v>
       </c>
       <c r="K228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N228">
@@ -37534,12 +37534,12 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ228">
@@ -37552,28 +37552,28 @@
         <v>0</v>
       </c>
       <c r="AM228">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN228">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO228">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP228">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ228">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR228">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS228">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT228">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
@@ -37613,10 +37613,10 @@
         </is>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -37625,14 +37625,14 @@
         <v>0</v>
       </c>
       <c r="K229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N229">
@@ -37697,12 +37697,12 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79"]</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ229">
@@ -37715,28 +37715,28 @@
         <v>0</v>
       </c>
       <c r="AM229">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN229">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO229">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP229">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ229">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR229">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AS229">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT229">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
@@ -38105,23 +38105,23 @@
         <v>0</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I232">
         <v>0</v>
       </c>
       <c r="J232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232">
         <v>0</v>
       </c>
       <c r="L232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N232">
@@ -38191,7 +38191,7 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "59", "90+8"]</t>
         </is>
       </c>
       <c r="AJ232">
@@ -38204,28 +38204,28 @@
         <v>0</v>
       </c>
       <c r="AM232">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN232">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AO232">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP232">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ232">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR232">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AS232">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT232">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
@@ -38265,26 +38265,26 @@
         </is>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L233">
         <v>0</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N233">
@@ -38349,12 +38349,12 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "57", "62"]</t>
         </is>
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AJ233">
@@ -38367,28 +38367,28 @@
         <v>0</v>
       </c>
       <c r="AM233">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN233">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO233">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP233">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ233">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR233">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS233">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT233">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
@@ -38591,13 +38591,13 @@
         </is>
       </c>
       <c r="G235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235">
         <v>0</v>
       </c>
       <c r="I235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235">
         <v>0</v>
@@ -38610,7 +38610,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N235">
@@ -38675,7 +38675,7 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
@@ -38693,28 +38693,28 @@
         <v>0</v>
       </c>
       <c r="AM235">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN235">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO235">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP235">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ235">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR235">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS235">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT235">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
@@ -38754,26 +38754,26 @@
         </is>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I236">
         <v>0</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N236">
@@ -38838,12 +38838,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "75"]</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "73"]</t>
         </is>
       </c>
       <c r="AJ236">
@@ -38856,28 +38856,28 @@
         <v>0</v>
       </c>
       <c r="AM236">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN236">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO236">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP236">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ236">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR236">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS236">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT236">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>0</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I237">
         <v>0</v>
@@ -38932,11 +38932,11 @@
         <v>0</v>
       </c>
       <c r="L237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N237">
@@ -39006,7 +39006,7 @@
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ237">
@@ -39019,28 +39019,28 @@
         <v>0</v>
       </c>
       <c r="AM237">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN237">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO237">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP237">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ237">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR237">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS237">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT237">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
@@ -39080,26 +39080,26 @@
         </is>
       </c>
       <c r="G238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238">
         <v>0</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N238">
@@ -39164,12 +39164,12 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "80"]</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "45"]</t>
         </is>
       </c>
       <c r="AJ238">
@@ -39182,28 +39182,28 @@
         <v>0</v>
       </c>
       <c r="AM238">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN238">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO238">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP238">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ238">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR238">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS238">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT238">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -39255,14 +39255,14 @@
         <v>0</v>
       </c>
       <c r="K239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L239">
         <v>0</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N239">
@@ -39327,7 +39327,7 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "71"]</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
@@ -39406,26 +39406,26 @@
         </is>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240">
         <v>0</v>
       </c>
       <c r="K240">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L240">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N240">
@@ -39490,12 +39490,12 @@
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "62", "74", "82"]</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "65", "87"]</t>
         </is>
       </c>
       <c r="AJ240">
@@ -39508,28 +39508,28 @@
         <v>0</v>
       </c>
       <c r="AM240">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN240">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO240">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP240">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ240">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR240">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS240">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT240">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
@@ -39569,26 +39569,26 @@
         </is>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K241">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N241">
@@ -39653,12 +39653,12 @@
       </c>
       <c r="AH241" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "49", "64", "86"]</t>
         </is>
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "54"]</t>
         </is>
       </c>
       <c r="AJ241">
@@ -39671,16 +39671,16 @@
         <v>0</v>
       </c>
       <c r="AM241">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN241">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO241">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP241">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ241">
         <v>0</v>
@@ -40058,26 +40058,26 @@
         </is>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K244">
         <v>0</v>
       </c>
       <c r="L244">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N244">
@@ -40142,12 +40142,12 @@
       </c>
       <c r="AH244" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "60", "66", "90+1"]</t>
         </is>
       </c>
       <c r="AJ244">
@@ -40160,28 +40160,28 @@
         <v>0</v>
       </c>
       <c r="AM244">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN244">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO244">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP244">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ244">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR244">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS244">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT244">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
@@ -41199,26 +41199,26 @@
         </is>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251">
         <v>0</v>
       </c>
       <c r="K251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N251">
@@ -41283,12 +41283,12 @@
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "59"]</t>
         </is>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "80"]</t>
         </is>
       </c>
       <c r="AJ251">
@@ -41301,28 +41301,28 @@
         <v>0</v>
       </c>
       <c r="AM251">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN251">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO251">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP251">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ251">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR251">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS251">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT251">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N252">
@@ -41464,28 +41464,28 @@
         <v>0</v>
       </c>
       <c r="AM252">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN252">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO252">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP252">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ252">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR252">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS252">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT252">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
@@ -41528,23 +41528,23 @@
         <v>0</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I253">
         <v>0</v>
       </c>
       <c r="J253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K253">
         <v>0</v>
       </c>
       <c r="L253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N253">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "35", "82"]</t>
         </is>
       </c>
       <c r="AJ253">
@@ -41627,28 +41627,28 @@
         <v>0</v>
       </c>
       <c r="AM253">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN253">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO253">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP253">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ253">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR253">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS253">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT253">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
@@ -41688,13 +41688,13 @@
         </is>
       </c>
       <c r="G254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -41703,11 +41703,11 @@
         <v>0</v>
       </c>
       <c r="L254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N254">
@@ -41772,12 +41772,12 @@
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ254">
@@ -41790,28 +41790,28 @@
         <v>0</v>
       </c>
       <c r="AM254">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN254">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO254">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP254">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ254">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR254">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS254">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT254">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
@@ -41851,13 +41851,13 @@
         </is>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J255">
         <v>0</v>
@@ -41866,11 +41866,11 @@
         <v>0</v>
       </c>
       <c r="L255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N255">
@@ -41935,12 +41935,12 @@
       </c>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AJ255">
@@ -41953,28 +41953,28 @@
         <v>0</v>
       </c>
       <c r="AM255">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN255">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO255">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP255">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ255">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AR255">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS255">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT255">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N256">
@@ -42116,28 +42116,28 @@
         <v>0</v>
       </c>
       <c r="AM256">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN256">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO256">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP256">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ256">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR256">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS256">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT256">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
@@ -42177,26 +42177,26 @@
         </is>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N257">
@@ -42261,12 +42261,12 @@
       </c>
       <c r="AH257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "56", "60"]</t>
         </is>
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "86"]</t>
         </is>
       </c>
       <c r="AJ257">
@@ -42279,28 +42279,28 @@
         <v>0</v>
       </c>
       <c r="AM257">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN257">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO257">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP257">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ257">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR257">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS257">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT257">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         </is>
       </c>
       <c r="G258">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -42352,14 +42352,14 @@
         <v>0</v>
       </c>
       <c r="K258">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L258">
         <v>0</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N258">
@@ -42424,7 +42424,7 @@
       </c>
       <c r="AH258" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "90+5"]</t>
         </is>
       </c>
       <c r="AI258" t="inlineStr">
@@ -42442,28 +42442,28 @@
         <v>0</v>
       </c>
       <c r="AM258">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN258">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO258">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP258">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ258">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR258">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AS258">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT258">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
@@ -42503,26 +42503,26 @@
         </is>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H259">
         <v>0</v>
       </c>
       <c r="I259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J259">
         <v>0</v>
       </c>
       <c r="K259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259">
         <v>0</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N259">
@@ -42535,7 +42535,7 @@
         <v>4.85</v>
       </c>
       <c r="Q259">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R259">
         <v>1.91</v>
@@ -42574,20 +42574,20 @@
         <v>4.5</v>
       </c>
       <c r="AD259">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE259">
         <v>1.04</v>
       </c>
       <c r="AF259">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG259">
         <v>1.57</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "53"]</t>
         </is>
       </c>
       <c r="AI259" t="inlineStr">
@@ -42605,28 +42605,28 @@
         <v>0</v>
       </c>
       <c r="AM259">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN259">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO259">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP259">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ259">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR259">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS259">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT259">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
@@ -42666,13 +42666,13 @@
         </is>
       </c>
       <c r="G260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H260">
         <v>0</v>
       </c>
       <c r="I260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -42685,11 +42685,11 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N260">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O260">
         <v>3</v>
@@ -42698,10 +42698,10 @@
         <v>4.6</v>
       </c>
       <c r="Q260">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="R260">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S260">
         <v>1.53</v>
@@ -42719,10 +42719,10 @@
         <v>1.03</v>
       </c>
       <c r="X260">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y260">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z260">
         <v>2.43</v>
@@ -42740,17 +42740,17 @@
         <v>1.11</v>
       </c>
       <c r="AE260">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF260">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG260">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr">
@@ -42768,28 +42768,28 @@
         <v>0</v>
       </c>
       <c r="AM260">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN260">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO260">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP260">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ260">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR260">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS260">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT260">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
@@ -42829,36 +42829,36 @@
         </is>
       </c>
       <c r="G261">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I261">
         <v>0</v>
       </c>
       <c r="J261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L261">
         <v>0</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N261">
         <v>4.4</v>
       </c>
       <c r="O261">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P261">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q261">
         <v>4.52</v>
@@ -42870,7 +42870,7 @@
         <v>1.33</v>
       </c>
       <c r="T261">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U261">
         <v>2.38</v>
@@ -42879,28 +42879,28 @@
         <v>1.46</v>
       </c>
       <c r="W261">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X261">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y261">
         <v>1.22</v>
       </c>
       <c r="Z261">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AA261">
         <v>1.7</v>
       </c>
       <c r="AB261">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC261">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD261">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE261">
         <v>1.17</v>
@@ -42913,46 +42913,46 @@
       </c>
       <c r="AH261" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "58"]</t>
         </is>
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ261">
         <v>1.25</v>
       </c>
       <c r="AK261">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL261">
         <v>0</v>
       </c>
       <c r="AM261">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN261">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO261">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP261">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ261">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR261">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS261">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT261">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
@@ -42992,26 +42992,26 @@
         </is>
       </c>
       <c r="G262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I262">
         <v>0</v>
       </c>
       <c r="J262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L262">
         <v>0</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N262">
@@ -43076,12 +43076,12 @@
       </c>
       <c r="AH262" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AJ262">
@@ -43094,16 +43094,16 @@
         <v>0</v>
       </c>
       <c r="AM262">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN262">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO262">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP262">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ262">
         <v>0</v>
@@ -43155,10 +43155,10 @@
         </is>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -43167,14 +43167,14 @@
         <v>0</v>
       </c>
       <c r="K263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N263">
@@ -43239,12 +43239,12 @@
       </c>
       <c r="AH263" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ263">
@@ -43257,28 +43257,28 @@
         <v>0</v>
       </c>
       <c r="AM263">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN263">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO263">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP263">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ263">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR263">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AS263">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT263">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
@@ -43318,26 +43318,26 @@
         </is>
       </c>
       <c r="G264">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H264">
         <v>0</v>
       </c>
       <c r="I264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264">
         <v>0</v>
       </c>
       <c r="K264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L264">
         <v>0</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N264">
@@ -43402,14 +43402,14 @@
       </c>
       <c r="AH264" t="inlineStr">
         <is>
+          <t>["28", "54", "90"]</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ264">
         <v>0</v>
       </c>
@@ -43420,28 +43420,28 @@
         <v>0</v>
       </c>
       <c r="AM264">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN264">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO264">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP264">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ264">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR264">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="AS264">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT264">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
@@ -43481,26 +43481,26 @@
         </is>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I265">
         <v>0</v>
       </c>
       <c r="J265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L265">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N265">
@@ -43565,12 +43565,12 @@
       </c>
       <c r="AH265" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI265" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "62", "73", "79", "90+6"]</t>
         </is>
       </c>
       <c r="AJ265">
@@ -43583,28 +43583,28 @@
         <v>0</v>
       </c>
       <c r="AM265">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN265">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO265">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP265">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AQ265">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR265">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AS265">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT265">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
@@ -43644,13 +43644,13 @@
         </is>
       </c>
       <c r="G266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H266">
         <v>0</v>
       </c>
       <c r="I266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -43663,11 +43663,11 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N266">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O266">
         <v>3.5</v>
@@ -43679,7 +43679,7 @@
         <v>3.25</v>
       </c>
       <c r="R266">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S266">
         <v>1.25</v>
@@ -43688,13 +43688,13 @@
         <v>3.6</v>
       </c>
       <c r="U266">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="V266">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W266">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X266">
         <v>1.03</v>
@@ -43703,7 +43703,7 @@
         <v>1.1</v>
       </c>
       <c r="Z266">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA266">
         <v>1.5</v>
@@ -43724,20 +43724,20 @@
         <v>1.44</v>
       </c>
       <c r="AG266">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
+          <t>["5", "45+1"]</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ266">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK266">
         <v>1.36</v>
@@ -43746,28 +43746,28 @@
         <v>0</v>
       </c>
       <c r="AM266">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN266">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO266">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP266">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ266">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR266">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS266">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT266">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
@@ -43807,26 +43807,26 @@
         </is>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I267">
         <v>0</v>
       </c>
       <c r="J267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L267">
         <v>0</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N267">
@@ -43891,12 +43891,12 @@
       </c>
       <c r="AH267" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85", "90"]</t>
         </is>
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AJ267">
@@ -43909,28 +43909,28 @@
         <v>0</v>
       </c>
       <c r="AM267">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN267">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO267">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP267">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ267">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR267">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS267">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT267">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
@@ -43970,26 +43970,26 @@
         </is>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J268">
         <v>0</v>
       </c>
       <c r="K268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N268">
@@ -44054,12 +44054,12 @@
       </c>
       <c r="AH268" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "78"]</t>
         </is>
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AJ268">
@@ -44072,28 +44072,28 @@
         <v>0</v>
       </c>
       <c r="AM268">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN268">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO268">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP268">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ268">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR268">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS268">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT268">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
@@ -44133,26 +44133,26 @@
         </is>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L269">
         <v>0</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N269">
@@ -44217,12 +44217,12 @@
       </c>
       <c r="AH269" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "48", "53", "72"]</t>
         </is>
       </c>
       <c r="AI269" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AJ269">
@@ -44235,28 +44235,28 @@
         <v>0</v>
       </c>
       <c r="AM269">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN269">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO269">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP269">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ269">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AR269">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS269">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT269">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
@@ -44296,26 +44296,26 @@
         </is>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H270">
         <v>0</v>
       </c>
       <c r="I270">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J270">
         <v>0</v>
       </c>
       <c r="K270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L270">
         <v>0</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N270">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="AH270" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "10", "45+2", "65", "84"]</t>
         </is>
       </c>
       <c r="AI270" t="inlineStr">
@@ -44398,28 +44398,28 @@
         <v>0</v>
       </c>
       <c r="AM270">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN270">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO270">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP270">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ270">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AR270">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS270">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT270">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
@@ -44459,16 +44459,16 @@
         </is>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K271">
         <v>0</v>
@@ -44478,50 +44478,50 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N271">
         <v>2.37</v>
       </c>
       <c r="O271">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P271">
         <v>3</v>
       </c>
       <c r="Q271">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="R271">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S271">
         <v>1.49</v>
       </c>
       <c r="T271">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="U271">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V271">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W271">
         <v>1.03</v>
       </c>
       <c r="X271">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y271">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="Z271">
         <v>2.55</v>
       </c>
       <c r="AA271">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AB271">
         <v>1.48</v>
@@ -44543,46 +44543,46 @@
       </c>
       <c r="AH271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "32"]</t>
         </is>
       </c>
       <c r="AI271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "39"]</t>
         </is>
       </c>
       <c r="AJ271">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK271">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL271">
         <v>0</v>
       </c>
       <c r="AM271">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN271">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO271">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP271">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ271">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR271">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS271">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT271">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
@@ -44648,52 +44648,52 @@
         <v>1.67</v>
       </c>
       <c r="O272">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P272">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q272">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="R272">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="S272">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="T272">
         <v>2.25</v>
       </c>
       <c r="U272">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="V272">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W272">
         <v>1.03</v>
       </c>
       <c r="X272">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y272">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Z272">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AA272">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AB272">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC272">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AD272">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE272">
         <v>1.03</v>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK272">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44785,7 +44785,7 @@
         </is>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -44797,14 +44797,14 @@
         <v>0</v>
       </c>
       <c r="K273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273">
         <v>0</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N273">
@@ -44869,7 +44869,7 @@
       </c>
       <c r="AH273" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI273" t="inlineStr">
@@ -44887,28 +44887,28 @@
         <v>0</v>
       </c>
       <c r="AM273">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN273">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO273">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP273">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ273">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR273">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS273">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT273">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
@@ -44948,26 +44948,26 @@
         </is>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I274">
         <v>0</v>
       </c>
       <c r="J274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L274">
         <v>0</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N274">
@@ -45032,12 +45032,12 @@
       </c>
       <c r="AH274" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "86"]</t>
         </is>
       </c>
       <c r="AI274" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ274">
@@ -45050,28 +45050,28 @@
         <v>0</v>
       </c>
       <c r="AM274">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN274">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO274">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP274">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ274">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR274">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS274">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT274">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
@@ -45114,13 +45114,13 @@
         <v>0</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I275">
         <v>0</v>
       </c>
       <c r="J275">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -45130,7 +45130,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N275">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "36"]</t>
         </is>
       </c>
       <c r="AJ275">
@@ -45213,28 +45213,28 @@
         <v>0</v>
       </c>
       <c r="AM275">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN275">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO275">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP275">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ275">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR275">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS275">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AT275">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
@@ -45274,13 +45274,13 @@
         </is>
       </c>
       <c r="G276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276">
         <v>0</v>
       </c>
       <c r="I276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J276">
         <v>0</v>
@@ -45293,7 +45293,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N276">
@@ -45306,7 +45306,7 @@
         <v>3.5</v>
       </c>
       <c r="Q276">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R276">
         <v>2</v>
@@ -45315,7 +45315,7 @@
         <v>1.4</v>
       </c>
       <c r="T276">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U276">
         <v>3.2</v>
@@ -45327,16 +45327,16 @@
         <v>1.05</v>
       </c>
       <c r="X276">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y276">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z276">
         <v>2.88</v>
       </c>
       <c r="AA276">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB276">
         <v>1.6</v>
@@ -45345,10 +45345,10 @@
         <v>3.6</v>
       </c>
       <c r="AD276">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE276">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF276">
         <v>1.93</v>
@@ -45358,7 +45358,7 @@
       </c>
       <c r="AH276" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AI276" t="inlineStr">
@@ -45370,34 +45370,34 @@
         <v>1.24</v>
       </c>
       <c r="AK276">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL276">
         <v>0</v>
       </c>
       <c r="AM276">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN276">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO276">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP276">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ276">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AR276">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS276">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT276">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
@@ -45428,22 +45428,22 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J277">
         <v>0</v>
@@ -45452,115 +45452,115 @@
         <v>0</v>
       </c>
       <c r="L277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N277">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O277">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="Q277">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R277">
         <v>2.1</v>
       </c>
       <c r="S277">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T277">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U277">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="V277">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W277">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y277">
         <v>1.29</v>
       </c>
       <c r="Z277">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA277">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB277">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AC277">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD277">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE277">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF277">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG277">
         <v>2</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "39"]</t>
         </is>
       </c>
       <c r="AI277" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "68"]</t>
         </is>
       </c>
       <c r="AJ277">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AK277">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL277">
         <v>0</v>
       </c>
       <c r="AM277">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN277">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO277">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP277">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ277">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR277">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS277">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT277">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G278">
@@ -45619,68 +45619,68 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N278">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="O278">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P278">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="Q278">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R278">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S278">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T278">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U278">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="V278">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W278">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X278">
         <v>1.04</v>
       </c>
       <c r="Y278">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z278">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA278">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AB278">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC278">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD278">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE278">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF278">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG278">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,37 +45693,37 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK278">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL278">
         <v>0</v>
       </c>
       <c r="AM278">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN278">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO278">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP278">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ278">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR278">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AS278">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT278">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G279">
@@ -45782,68 +45782,68 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N279">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O279">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P279">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="Q279">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="R279">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S279">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T279">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U279">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V279">
         <v>1.44</v>
       </c>
       <c r="W279">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X279">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y279">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z279">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA279">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AB279">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC279">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD279">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AE279">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF279">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG279">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,37 +45856,37 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK279">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AL279">
         <v>0</v>
       </c>
       <c r="AM279">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN279">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO279">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP279">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ279">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR279">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS279">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT279">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
@@ -45917,16 +45917,16 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -45938,118 +45938,118 @@
         <v>0</v>
       </c>
       <c r="K280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L280">
         <v>0</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N280">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="O280">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P280">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="Q280">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R280">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S280">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T280">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U280">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="V280">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W280">
         <v>1.07</v>
       </c>
       <c r="X280">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y280">
         <v>1.29</v>
       </c>
       <c r="Z280">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="AA280">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB280">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC280">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="AD280">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE280">
         <v>1.07</v>
       </c>
       <c r="AF280">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG280">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
+          <t>["74"]</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ280">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK280">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AL280">
         <v>0</v>
       </c>
       <c r="AM280">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN280">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO280">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP280">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ280">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR280">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS280">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT280">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
@@ -46089,26 +46089,26 @@
         </is>
       </c>
       <c r="G281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281">
         <v>0</v>
       </c>
       <c r="L281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N281">
@@ -46173,12 +46173,12 @@
       </c>
       <c r="AH281" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AI281" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "61"]</t>
         </is>
       </c>
       <c r="AJ281">
@@ -46191,28 +46191,28 @@
         <v>0</v>
       </c>
       <c r="AM281">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN281">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO281">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP281">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ281">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR281">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS281">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT281">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
@@ -46252,13 +46252,13 @@
         </is>
       </c>
       <c r="G282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J282">
         <v>0</v>
@@ -46267,11 +46267,11 @@
         <v>0</v>
       </c>
       <c r="L282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N282">
@@ -46336,12 +46336,12 @@
       </c>
       <c r="AH282" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25"]</t>
         </is>
       </c>
       <c r="AI282" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AJ282">
@@ -46354,28 +46354,28 @@
         <v>0</v>
       </c>
       <c r="AM282">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN282">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO282">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP282">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ282">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR282">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS282">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT282">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
@@ -46415,26 +46415,26 @@
         </is>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H283">
         <v>0</v>
       </c>
       <c r="I283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J283">
         <v>0</v>
       </c>
       <c r="K283">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L283">
         <v>0</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N283">
@@ -46499,14 +46499,14 @@
       </c>
       <c r="AH283" t="inlineStr">
         <is>
+          <t>["3", "7", "65", "88", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ283">
         <v>0</v>
       </c>
@@ -46517,28 +46517,28 @@
         <v>0</v>
       </c>
       <c r="AM283">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN283">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO283">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP283">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ283">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AR283">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS283">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT283">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N284">
@@ -46680,28 +46680,28 @@
         <v>0</v>
       </c>
       <c r="AM284">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN284">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO284">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP284">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ284">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR284">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS284">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT284">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
@@ -46732,139 +46732,139 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K285">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L285">
         <v>0</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N285">
-        <v>1.86</v>
+        <v>2.7</v>
       </c>
       <c r="O285">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P285">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q285">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="R285">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S285">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T285">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U285">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="V285">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W285">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X285">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y285">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z285">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA285">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AB285">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AC285">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD285">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AE285">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF285">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG285">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "90", "90+7"]</t>
         </is>
       </c>
       <c r="AI285" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ285">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK285">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AL285">
         <v>0</v>
       </c>
       <c r="AM285">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN285">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO285">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP285">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ285">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR285">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS285">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT285">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
@@ -46895,139 +46895,139 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G286">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L286">
         <v>0</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N286">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="O286">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P286">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q286">
-        <v>3.47</v>
+        <v>2.5</v>
       </c>
       <c r="R286">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="S286">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T286">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U286">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="V286">
+        <v>1.39</v>
+      </c>
+      <c r="W286">
+        <v>1.03</v>
+      </c>
+      <c r="X286">
+        <v>1.05</v>
+      </c>
+      <c r="Y286">
         <v>1.29</v>
       </c>
-      <c r="W286">
-        <v>1.01</v>
-      </c>
-      <c r="X286">
+      <c r="Z286">
+        <v>3.5</v>
+      </c>
+      <c r="AA286">
+        <v>1.85</v>
+      </c>
+      <c r="AB286">
+        <v>1.8</v>
+      </c>
+      <c r="AC286">
+        <v>3.4</v>
+      </c>
+      <c r="AD286">
+        <v>1.3</v>
+      </c>
+      <c r="AE286">
         <v>1.1</v>
       </c>
-      <c r="Y286">
-        <v>1.44</v>
-      </c>
-      <c r="Z286">
-        <v>2.45</v>
-      </c>
-      <c r="AA286">
-        <v>2.45</v>
-      </c>
-      <c r="AB286">
-        <v>1.44</v>
-      </c>
-      <c r="AC286">
-        <v>4.45</v>
-      </c>
-      <c r="AD286">
-        <v>1.14</v>
-      </c>
-      <c r="AE286">
-        <v>1.04</v>
-      </c>
       <c r="AF286">
+        <v>1.75</v>
+      </c>
+      <c r="AG286">
+        <v>1.91</v>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>["4", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>["34"]</t>
+        </is>
+      </c>
+      <c r="AJ286">
+        <v>1.25</v>
+      </c>
+      <c r="AK286">
+        <v>1.77</v>
+      </c>
+      <c r="AL286">
+        <v>0</v>
+      </c>
+      <c r="AM286">
+        <v>4</v>
+      </c>
+      <c r="AN286">
         <v>2</v>
       </c>
-      <c r="AG286">
-        <v>1.7</v>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ286">
-        <v>1.36</v>
-      </c>
-      <c r="AK286">
-        <v>1.4</v>
-      </c>
-      <c r="AL286">
-        <v>0</v>
-      </c>
-      <c r="AM286">
-        <v>-1</v>
-      </c>
-      <c r="AN286">
-        <v>-1</v>
-      </c>
       <c r="AO286">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP286">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ286">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR286">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS286">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT286">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>0</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I287">
         <v>0</v>
@@ -47082,11 +47082,11 @@
         <v>0</v>
       </c>
       <c r="L287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N287">
@@ -47156,7 +47156,7 @@
       </c>
       <c r="AI287" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "90+7"]</t>
         </is>
       </c>
       <c r="AJ287">
@@ -47169,28 +47169,28 @@
         <v>0</v>
       </c>
       <c r="AM287">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN287">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO287">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP287">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ287">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR287">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS287">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT287">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
@@ -47556,26 +47556,26 @@
         </is>
       </c>
       <c r="G290">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I290">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J290">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K290">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L290">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N290">
@@ -47640,12 +47640,12 @@
       </c>
       <c r="AH290" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "32", "75"]</t>
         </is>
       </c>
       <c r="AI290" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "43", "87", "90+4"]</t>
         </is>
       </c>
       <c r="AJ290">
@@ -47658,28 +47658,28 @@
         <v>0</v>
       </c>
       <c r="AM290">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN290">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO290">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP290">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ290">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR290">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS290">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT290">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
@@ -47722,60 +47722,60 @@
         <v>0</v>
       </c>
       <c r="H291">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I291">
         <v>0</v>
       </c>
       <c r="J291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291">
         <v>0</v>
       </c>
       <c r="L291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N291">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="O291">
         <v>3.4</v>
       </c>
       <c r="P291">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q291">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="R291">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="S291">
         <v>1.3</v>
       </c>
       <c r="T291">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U291">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="V291">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W291">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X291">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z291">
         <v>4.33</v>
@@ -47799,7 +47799,7 @@
         <v>1.57</v>
       </c>
       <c r="AG291">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
       </c>
       <c r="AI291" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "61", "90"]</t>
         </is>
       </c>
       <c r="AJ291">
@@ -47821,28 +47821,28 @@
         <v>0</v>
       </c>
       <c r="AM291">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN291">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO291">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP291">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ291">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR291">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS291">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT291">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>0</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I293">
         <v>0</v>
@@ -48060,11 +48060,11 @@
         <v>0</v>
       </c>
       <c r="L293">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N293">
@@ -48134,7 +48134,7 @@
       </c>
       <c r="AI293" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "70"]</t>
         </is>
       </c>
       <c r="AJ293">
@@ -48147,28 +48147,28 @@
         <v>0</v>
       </c>
       <c r="AM293">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN293">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO293">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP293">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ293">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AR293">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AS293">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT293">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
@@ -48227,14 +48227,14 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N294">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O294">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P294">
         <v>1.99</v>
@@ -48243,13 +48243,13 @@
         <v>4.4</v>
       </c>
       <c r="R294">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S294">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="T294">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="U294">
         <v>2.95</v>
@@ -48264,19 +48264,19 @@
         <v>1.06</v>
       </c>
       <c r="Y294">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Z294">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AA294">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AB294">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC294">
-        <v>4.44</v>
+        <v>4.67</v>
       </c>
       <c r="AD294">
         <v>1.22</v>
@@ -48288,7 +48288,7 @@
         <v>1.91</v>
       </c>
       <c r="AG294">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48310,28 +48310,28 @@
         <v>0</v>
       </c>
       <c r="AM294">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN294">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO294">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP294">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ294">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR294">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AS294">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT294">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
@@ -48371,26 +48371,26 @@
         </is>
       </c>
       <c r="G295">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I295">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J295">
         <v>0</v>
       </c>
       <c r="K295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N295">
@@ -48455,12 +48455,12 @@
       </c>
       <c r="AH295" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "17", "35", "90+1"]</t>
         </is>
       </c>
       <c r="AI295" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ295">
@@ -48473,28 +48473,28 @@
         <v>0</v>
       </c>
       <c r="AM295">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN295">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO295">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP295">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ295">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AR295">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS295">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT295">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         </is>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H296">
         <v>0</v>
@@ -48546,24 +48546,24 @@
         <v>0</v>
       </c>
       <c r="K296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296">
         <v>0</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48618,14 +48618,14 @@
       </c>
       <c r="AH296" t="inlineStr">
         <is>
+          <t>["90+4"]</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI296" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ296">
         <v>0</v>
       </c>
@@ -48636,28 +48636,28 @@
         <v>0</v>
       </c>
       <c r="AM296">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN296">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO296">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP296">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ296">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR296">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS296">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT296">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
@@ -48697,26 +48697,26 @@
         </is>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J297">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K297">
         <v>0</v>
       </c>
       <c r="L297">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N297">
@@ -48781,12 +48781,12 @@
       </c>
       <c r="AH297" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AI297" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "45+1", "66", "90+7"]</t>
         </is>
       </c>
       <c r="AJ297">
@@ -48799,28 +48799,28 @@
         <v>0</v>
       </c>
       <c r="AM297">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN297">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO297">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP297">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ297">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR297">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS297">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT297">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
@@ -48860,26 +48860,26 @@
         </is>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H298">
         <v>0</v>
       </c>
       <c r="I298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J298">
         <v>0</v>
       </c>
       <c r="K298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L298">
         <v>0</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N298">
@@ -48944,7 +48944,7 @@
       </c>
       <c r="AH298" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "54", "90+2"]</t>
         </is>
       </c>
       <c r="AI298" t="inlineStr">
@@ -48962,28 +48962,28 @@
         <v>0</v>
       </c>
       <c r="AM298">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN298">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO298">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP298">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ298">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR298">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS298">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT298">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
@@ -49061,10 +49061,10 @@
         <v>1.97</v>
       </c>
       <c r="S299">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T299">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U299">
         <v>2.75</v>
@@ -49079,10 +49079,10 @@
         <v>1.07</v>
       </c>
       <c r="Y299">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z299">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA299">
         <v>1.92</v>
@@ -49091,10 +49091,10 @@
         <v>1.77</v>
       </c>
       <c r="AC299">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="AD299">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE299">
         <v>1.06</v>
@@ -49103,7 +49103,7 @@
         <v>1.83</v>
       </c>
       <c r="AG299">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49372,19 +49372,19 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O301">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P301">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q301">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R301">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S301">
         <v>1.5</v>
@@ -49402,34 +49402,34 @@
         <v>1.04</v>
       </c>
       <c r="X301">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y301">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z301">
+        <v>2.43</v>
+      </c>
+      <c r="AA301">
         <v>2.46</v>
       </c>
-      <c r="AA301">
-        <v>2.44</v>
-      </c>
       <c r="AB301">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC301">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD301">
         <v>1.12</v>
       </c>
       <c r="AE301">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF301">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AG301">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>1.22</v>
       </c>
       <c r="AK301">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49535,10 +49535,10 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O302">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P302">
         <v>5.8</v>
@@ -49592,7 +49592,7 @@
         <v>2.05</v>
       </c>
       <c r="AG302">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49698,55 +49698,55 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O303">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P303">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q303">
         <v>3</v>
       </c>
       <c r="R303">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="S303">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="T303">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U303">
         <v>3.52</v>
       </c>
       <c r="V303">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W303">
         <v>1.04</v>
       </c>
       <c r="X303">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y303">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Z303">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AA303">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AB303">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC303">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="AD303">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE303">
         <v>1.03</v>
@@ -49861,58 +49861,58 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="O304">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P304">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="Q304">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R304">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S304">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T304">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U304">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V304">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W304">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X304">
         <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z304">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA304">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB304">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC304">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AD304">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE304">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF304">
         <v>1.5</v>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK304">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,80 +50024,80 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="O305">
+        <v>5.75</v>
+      </c>
+      <c r="P305">
+        <v>7</v>
+      </c>
+      <c r="Q305">
+        <v>1.59</v>
+      </c>
+      <c r="R305">
+        <v>2.84</v>
+      </c>
+      <c r="S305">
+        <v>1.14</v>
+      </c>
+      <c r="T305">
+        <v>4.9</v>
+      </c>
+      <c r="U305">
+        <v>1.67</v>
+      </c>
+      <c r="V305">
+        <v>1.89</v>
+      </c>
+      <c r="W305">
+        <v>1.33</v>
+      </c>
+      <c r="X305">
+        <v>1.01</v>
+      </c>
+      <c r="Y305">
+        <v>1.01</v>
+      </c>
+      <c r="Z305">
+        <v>8</v>
+      </c>
+      <c r="AA305">
+        <v>1.22</v>
+      </c>
+      <c r="AB305">
+        <v>3.6</v>
+      </c>
+      <c r="AC305">
+        <v>1.6</v>
+      </c>
+      <c r="AD305">
+        <v>2.2</v>
+      </c>
+      <c r="AE305">
+        <v>1.5</v>
+      </c>
+      <c r="AF305">
+        <v>1.5</v>
+      </c>
+      <c r="AG305">
+        <v>2.4</v>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ305">
+        <v>1.02</v>
+      </c>
+      <c r="AK305">
         <v>3.75</v>
-      </c>
-      <c r="P305">
-        <v>5.25</v>
-      </c>
-      <c r="Q305">
-        <v>2.2</v>
-      </c>
-      <c r="R305">
-        <v>2.06</v>
-      </c>
-      <c r="S305">
-        <v>1.36</v>
-      </c>
-      <c r="T305">
-        <v>2.73</v>
-      </c>
-      <c r="U305">
-        <v>3.06</v>
-      </c>
-      <c r="V305">
-        <v>1.36</v>
-      </c>
-      <c r="W305">
-        <v>1.04</v>
-      </c>
-      <c r="X305">
-        <v>1.05</v>
-      </c>
-      <c r="Y305">
-        <v>1.33</v>
-      </c>
-      <c r="Z305">
-        <v>3.25</v>
-      </c>
-      <c r="AA305">
-        <v>2</v>
-      </c>
-      <c r="AB305">
-        <v>1.77</v>
-      </c>
-      <c r="AC305">
-        <v>3.85</v>
-      </c>
-      <c r="AD305">
-        <v>1.28</v>
-      </c>
-      <c r="AE305">
-        <v>1.05</v>
-      </c>
-      <c r="AF305">
-        <v>1.93</v>
-      </c>
-      <c r="AG305">
-        <v>1.83</v>
-      </c>
-      <c r="AH305" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI305" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ305">
-        <v>1.2</v>
-      </c>
-      <c r="AK305">
-        <v>2.28</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-09-12 18:30:00</t>
+          <t>2026-09-12 18:15:00</t>
         </is>
       </c>
     </row>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="O306">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="P306">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="Q306">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="R306">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="S306">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T306">
-        <v>4.9</v>
+        <v>2.73</v>
       </c>
       <c r="U306">
-        <v>1.82</v>
+        <v>3.06</v>
       </c>
       <c r="V306">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="W306">
+        <v>1.04</v>
+      </c>
+      <c r="X306">
+        <v>1.05</v>
+      </c>
+      <c r="Y306">
+        <v>1.33</v>
+      </c>
+      <c r="Z306">
+        <v>3.25</v>
+      </c>
+      <c r="AA306">
+        <v>2</v>
+      </c>
+      <c r="AB306">
+        <v>1.77</v>
+      </c>
+      <c r="AC306">
+        <v>3.85</v>
+      </c>
+      <c r="AD306">
         <v>1.28</v>
       </c>
-      <c r="X306">
-        <v>1.01</v>
-      </c>
-      <c r="Y306">
-        <v>1.02</v>
-      </c>
-      <c r="Z306">
-        <v>7.9</v>
-      </c>
-      <c r="AA306">
-        <v>1.22</v>
-      </c>
-      <c r="AB306">
-        <v>3.8</v>
-      </c>
-      <c r="AC306">
-        <v>1.65</v>
-      </c>
-      <c r="AD306">
-        <v>2.07</v>
-      </c>
       <c r="AE306">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="AF306">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AG306">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AK306">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50350,16 +50350,16 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="O307">
         <v>3</v>
       </c>
       <c r="P307">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q307">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="R307">
         <v>2</v>
@@ -50368,7 +50368,7 @@
         <v>1.4</v>
       </c>
       <c r="T307">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="U307">
         <v>3.2</v>
@@ -50377,7 +50377,7 @@
         <v>1.3</v>
       </c>
       <c r="W307">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X307">
         <v>1.04</v>
@@ -50407,7 +50407,7 @@
         <v>1.85</v>
       </c>
       <c r="AG307">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AK307">
         <v>1.44</v>
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O308">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P308">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q308">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R308">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S308">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T308">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="U308">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V308">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W308">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X308">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y308">
         <v>1.4</v>
       </c>
       <c r="Z308">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA308">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB308">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC308">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD308">
         <v>1.19</v>
       </c>
       <c r="AE308">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF308">
         <v>2</v>
       </c>
       <c r="AG308">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK308">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="O311">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P311">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q311">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="R311">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="S311">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T311">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U311">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="V311">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W311">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X311">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z311">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA311">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AB311">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AC311">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD311">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE311">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF311">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG311">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK311">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,64 +51165,64 @@
         </is>
       </c>
       <c r="N312">
-        <v>4.85</v>
+        <v>1.68</v>
       </c>
       <c r="O312">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P312">
-        <v>1.55</v>
+        <v>4.33</v>
       </c>
       <c r="Q312">
-        <v>4.8</v>
+        <v>2.27</v>
       </c>
       <c r="R312">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S312">
+        <v>1.34</v>
+      </c>
+      <c r="T312">
+        <v>3</v>
+      </c>
+      <c r="U312">
+        <v>2.58</v>
+      </c>
+      <c r="V312">
+        <v>1.41</v>
+      </c>
+      <c r="W312">
+        <v>1.08</v>
+      </c>
+      <c r="X312">
+        <v>1.03</v>
+      </c>
+      <c r="Y312">
         <v>1.25</v>
       </c>
-      <c r="T312">
-        <v>3.4</v>
-      </c>
-      <c r="U312">
-        <v>2.26</v>
-      </c>
-      <c r="V312">
-        <v>1.53</v>
-      </c>
-      <c r="W312">
+      <c r="Z312">
+        <v>3.6</v>
+      </c>
+      <c r="AA312">
+        <v>1.9</v>
+      </c>
+      <c r="AB312">
+        <v>1.9</v>
+      </c>
+      <c r="AC312">
+        <v>3.25</v>
+      </c>
+      <c r="AD312">
+        <v>1.3</v>
+      </c>
+      <c r="AE312">
         <v>1.12</v>
       </c>
-      <c r="X312">
-        <v>1.02</v>
-      </c>
-      <c r="Y312">
-        <v>1.18</v>
-      </c>
-      <c r="Z312">
-        <v>4.05</v>
-      </c>
-      <c r="AA312">
-        <v>1.63</v>
-      </c>
-      <c r="AB312">
-        <v>2.1</v>
-      </c>
-      <c r="AC312">
-        <v>2.63</v>
-      </c>
-      <c r="AD312">
-        <v>1.44</v>
-      </c>
-      <c r="AE312">
-        <v>1.14</v>
-      </c>
       <c r="AF312">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG312">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK312">
-        <v>1.15</v>
+        <v>2.05</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,19 +51491,19 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.53</v>
+        <v>4.85</v>
       </c>
       <c r="O314">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P314">
+        <v>1.55</v>
+      </c>
+      <c r="Q314">
         <v>4.8</v>
       </c>
-      <c r="Q314">
-        <v>2.05</v>
-      </c>
       <c r="R314">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="S314">
         <v>1.25</v>
@@ -51512,59 +51512,59 @@
         <v>3.4</v>
       </c>
       <c r="U314">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V314">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W314">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X314">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y314">
+        <v>1.18</v>
+      </c>
+      <c r="Z314">
+        <v>4.05</v>
+      </c>
+      <c r="AA314">
+        <v>1.63</v>
+      </c>
+      <c r="AB314">
+        <v>2.1</v>
+      </c>
+      <c r="AC314">
+        <v>2.63</v>
+      </c>
+      <c r="AD314">
+        <v>1.44</v>
+      </c>
+      <c r="AE314">
+        <v>1.14</v>
+      </c>
+      <c r="AF314">
+        <v>1.67</v>
+      </c>
+      <c r="AG314">
+        <v>2.07</v>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ314">
+        <v>2.16</v>
+      </c>
+      <c r="AK314">
         <v>1.15</v>
-      </c>
-      <c r="Z314">
-        <v>4.6</v>
-      </c>
-      <c r="AA314">
-        <v>1.58</v>
-      </c>
-      <c r="AB314">
-        <v>2.33</v>
-      </c>
-      <c r="AC314">
-        <v>2.38</v>
-      </c>
-      <c r="AD314">
-        <v>1.5</v>
-      </c>
-      <c r="AE314">
-        <v>1.16</v>
-      </c>
-      <c r="AF314">
-        <v>1.62</v>
-      </c>
-      <c r="AG314">
-        <v>2.1</v>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ314">
-        <v>1.1</v>
-      </c>
-      <c r="AK314">
-        <v>2.24</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51820,7 +51820,7 @@
         <v>2.87</v>
       </c>
       <c r="O316">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P316">
         <v>2.21</v>
@@ -51835,7 +51835,7 @@
         <v>1.29</v>
       </c>
       <c r="T316">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U316">
         <v>2.36</v>
@@ -51980,64 +51980,64 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O317">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P317">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q317">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R317">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S317">
         <v>1.29</v>
       </c>
       <c r="T317">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U317">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V317">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W317">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X317">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y317">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z317">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA317">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB317">
         <v>2.05</v>
       </c>
       <c r="AC317">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD317">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE317">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF317">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG317">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK317">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -53284,43 +53284,43 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O325">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P325">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q325">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="R325">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="S325">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T325">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="U325">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V325">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W325">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X325">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y325">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z325">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA325">
         <v>1.28</v>
@@ -53338,10 +53338,10 @@
         <v>1.38</v>
       </c>
       <c r="AF325">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG325">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK325">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53447,22 +53447,22 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O326">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P326">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q326">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R326">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S326">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T326">
         <v>2.8</v>
@@ -53471,34 +53471,34 @@
         <v>2.75</v>
       </c>
       <c r="V326">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W326">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X326">
         <v>1.05</v>
       </c>
       <c r="Y326">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z326">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA326">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB326">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC326">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AD326">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE326">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF326">
         <v>1.95</v>
@@ -53520,7 +53520,7 @@
         <v>1.13</v>
       </c>
       <c r="AK326">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,64 +54914,64 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="O335">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P335">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="Q335">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R335">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S335">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T335">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U335">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V335">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W335">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X335">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y335">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z335">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="AA335">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB335">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AC335">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AD335">
         <v>1.34</v>
       </c>
       <c r="AE335">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF335">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG335">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK335">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="O336">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P336">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="Q336">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R336">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S336">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T336">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U336">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V336">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W336">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X336">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y336">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z336">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="AA336">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB336">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AC336">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AD336">
         <v>1.34</v>
       </c>
       <c r="AE336">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF336">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG336">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK336">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AL336">
         <v>0</v>
